--- a/stock.xlsx
+++ b/stock.xlsx
@@ -672,7 +672,11 @@
           <t>G-1</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n"/>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>테스트</t>
+        </is>
+      </c>
       <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="n"/>

--- a/stock.xlsx
+++ b/stock.xlsx
@@ -672,11 +672,7 @@
           <t>G-1</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>테스트</t>
-        </is>
-      </c>
+      <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="n"/>

--- a/stock.xlsx
+++ b/stock.xlsx
@@ -40281,11 +40281,7 @@
       <c r="H151" s="2" t="n"/>
       <c r="I151" s="2" t="n"/>
       <c r="J151" s="2" t="n"/>
-      <c r="K151" s="2" t="inlineStr">
-        <is>
-          <t>E-8</t>
-        </is>
-      </c>
+      <c r="K151" s="2" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -40473,11 +40469,7 @@
       <c r="H159" s="2" t="n"/>
       <c r="I159" s="2" t="n"/>
       <c r="J159" s="2" t="n"/>
-      <c r="K159" s="2" t="inlineStr">
-        <is>
-          <t>E-8</t>
-        </is>
-      </c>
+      <c r="K159" s="2" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -40498,11 +40490,7 @@
       <c r="H160" s="2" t="n"/>
       <c r="I160" s="2" t="n"/>
       <c r="J160" s="2" t="n"/>
-      <c r="K160" s="2" t="inlineStr">
-        <is>
-          <t>E-8</t>
-        </is>
-      </c>
+      <c r="K160" s="2" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">

--- a/stock.xlsx
+++ b/stock.xlsx
@@ -40323,11 +40323,7 @@
       <c r="H153" s="2" t="n"/>
       <c r="I153" s="2" t="n"/>
       <c r="J153" s="2" t="n"/>
-      <c r="K153" s="2" t="inlineStr">
-        <is>
-          <t>G-8</t>
-        </is>
-      </c>
+      <c r="K153" s="2" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -40511,11 +40507,7 @@
       <c r="H161" s="2" t="n"/>
       <c r="I161" s="2" t="n"/>
       <c r="J161" s="2" t="n"/>
-      <c r="K161" s="2" t="inlineStr">
-        <is>
-          <t>G-8</t>
-        </is>
-      </c>
+      <c r="K161" s="2" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -40536,11 +40528,7 @@
       <c r="H162" s="2" t="n"/>
       <c r="I162" s="2" t="n"/>
       <c r="J162" s="2" t="n"/>
-      <c r="K162" s="2" t="inlineStr">
-        <is>
-          <t>G-8</t>
-        </is>
-      </c>
+      <c r="K162" s="2" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -40561,11 +40549,7 @@
       <c r="H163" s="2" t="n"/>
       <c r="I163" s="2" t="n"/>
       <c r="J163" s="2" t="n"/>
-      <c r="K163" s="2" t="inlineStr">
-        <is>
-          <t>I-8</t>
-        </is>
-      </c>
+      <c r="K163" s="2" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">

--- a/stock.xlsx
+++ b/stock.xlsx
@@ -40281,7 +40281,11 @@
       <c r="H151" s="2" t="n"/>
       <c r="I151" s="2" t="n"/>
       <c r="J151" s="2" t="n"/>
-      <c r="K151" s="2" t="n"/>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>E-8</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -40465,7 +40469,11 @@
       <c r="H159" s="2" t="n"/>
       <c r="I159" s="2" t="n"/>
       <c r="J159" s="2" t="n"/>
-      <c r="K159" s="2" t="n"/>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>E-8</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -40486,7 +40494,11 @@
       <c r="H160" s="2" t="n"/>
       <c r="I160" s="2" t="n"/>
       <c r="J160" s="2" t="n"/>
-      <c r="K160" s="2" t="n"/>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>E-8</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">

--- a/stock.xlsx
+++ b/stock.xlsx
@@ -29917,7 +29917,11 @@
       <c r="F161" s="2" t="n"/>
       <c r="G161" s="2" t="n"/>
       <c r="H161" s="2" t="n"/>
-      <c r="I161" s="2" t="n"/>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>A-9</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -29936,7 +29940,11 @@
       <c r="F162" s="2" t="n"/>
       <c r="G162" s="2" t="n"/>
       <c r="H162" s="2" t="n"/>
-      <c r="I162" s="2" t="n"/>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>A-9</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -29955,7 +29963,11 @@
       <c r="F163" s="2" t="n"/>
       <c r="G163" s="2" t="n"/>
       <c r="H163" s="2" t="n"/>
-      <c r="I163" s="2" t="n"/>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>A-9</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -29974,7 +29986,11 @@
       <c r="F164" s="2" t="n"/>
       <c r="G164" s="2" t="n"/>
       <c r="H164" s="2" t="n"/>
-      <c r="I164" s="2" t="n"/>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>A-9</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -29993,7 +30009,11 @@
       <c r="F165" s="2" t="n"/>
       <c r="G165" s="2" t="n"/>
       <c r="H165" s="2" t="n"/>
-      <c r="I165" s="2" t="n"/>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>A-9</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -30012,7 +30032,11 @@
       <c r="F166" s="2" t="n"/>
       <c r="G166" s="2" t="n"/>
       <c r="H166" s="2" t="n"/>
-      <c r="I166" s="2" t="n"/>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>A-9</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -30031,7 +30055,11 @@
       <c r="F167" s="2" t="n"/>
       <c r="G167" s="2" t="n"/>
       <c r="H167" s="2" t="n"/>
-      <c r="I167" s="2" t="n"/>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>A-9</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -30050,7 +30078,11 @@
       <c r="F168" s="2" t="n"/>
       <c r="G168" s="2" t="n"/>
       <c r="H168" s="2" t="n"/>
-      <c r="I168" s="2" t="n"/>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>A-9</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">

--- a/stock.xlsx
+++ b/stock.xlsx
@@ -29892,9 +29892,17 @@
           <t>A-9</t>
         </is>
       </c>
-      <c r="C160" s="2" t="n"/>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>hIL-2</t>
+        </is>
+      </c>
       <c r="D160" s="2" t="n"/>
-      <c r="E160" s="2" t="n"/>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>200ng/ul</t>
+        </is>
+      </c>
       <c r="F160" s="2" t="n"/>
       <c r="G160" s="2" t="n"/>
       <c r="H160" s="2" t="n"/>
